--- a/eastel-report-scripts/reports-pipelines/report-generation-mongo/2-Invoice-Recon/2-Invoice-Recon-actual-queries-used-output-file.xlsx
+++ b/eastel-report-scripts/reports-pipelines/report-generation-mongo/2-Invoice-Recon/2-Invoice-Recon-actual-queries-used-output-file.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -433,6 +433,199 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Q014</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>D:\DB_repos\eastel-reports\eastel-report-scripts\reports-pipelines\report-generation-mongo\2-Invoice-Recon\queries\14.js</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/*
+Query 14: Premium and special numbers.
+Output columns:
+- service_type
+- charge_type
+- call_type
+- no_of_calls
+- mou
+*/
+db.usage_logs.aggregate([
+  {
+    $match: {
+      usage_start_time: {
+        $gte: ISODate("2026-04-01T00:00:00Z"),
+        $lt: ISODate("2026-05-01T00:00:00Z")
+      },
+      rat_type: "VO",
+      service_type_sub_cd: "MO",
+      roaming_destination_id: 87,
+      act_usage_unit: { $gt: 0 },
+      $or: [
+        { opposite_number: "600380008000" },
+        { opposite_number: "60103" },
+        { opposite_number: "60100" },
+        { opposite_number: "6015454" },
+        { opposite_number: "6015300" },
+        { opposite_number: "6015353" },
+        { opposite_number: "6015404" },
+        { opposite_number: "6015444" },
+        { opposite_number: "6015777" },
+        { opposite_number: "6015555" },
+        { opposite_number: "6015999" },
+        { opposite_number: "6013504" },
+        { opposite_number: "6015511" },
+        { opposite_number: "6015800" },
+        { opposite_number: "6015995" },
+        { opposite_number: { $regex: "^601300" } },
+        { opposite_number: { $regex: "^601700" } },
+        { opposite_number: { $regex: "^601800" } }
+      ]
+    }
+  },
+  {
+    $addFields: {
+      call_type: {
+        $switch: {
+          branches: [
+            { case: { $eq: ["$opposite_number", "600380008000"] }, then: "1 MOCC - 03-8000 8000" },
+            {
+              case: {
+                $and: [
+                  { $regexMatch: { input: { $ifNull: ["$opposite_number", ""] }, regex: "^601300" } },
+                  { $lt: [{ $strLenCP: { $ifNull: ["$opposite_number", ""] } }, 12] }
+                ]
+              },
+              then: "1300 Numbers"
+            },
+            {
+              case: {
+                $and: [
+                  { $regexMatch: { input: { $ifNull: ["$opposite_number", ""] }, regex: "^601700" } },
+                  { $lt: [{ $strLenCP: { $ifNull: ["$opposite_number", ""] } }, 12] }
+                ]
+              },
+              then: "1700 Numbers"
+            },
+            {
+              case: {
+                $and: [
+                  { $regexMatch: { input: { $ifNull: ["$opposite_number", ""] }, regex: "^601800" } },
+                  { $lt: [{ $strLenCP: { $ifNull: ["$opposite_number", ""] } }, 12] }
+                ]
+              },
+              then: "1800 Numbers"
+            },
+            { case: { $eq: ["$opposite_number", "60103"] }, then: "Directory Assistance -Services 103" },
+            { case: { $eq: ["$opposite_number", "60100"] }, then: "Info Services - 100" },
+            { case: { $eq: ["$opposite_number", "6015454"] }, then: "Info Services - 15454" },
+            { case: { $eq: ["$opposite_number", "6015300"] }, then: "Info Services - 15300" },
+            { case: { $eq: ["$opposite_number", "6015353"] }, then: "Info Services - 15353" },
+            { case: { $eq: ["$opposite_number", "6015404"] }, then: "Info Services - 15404" },
+            { case: { $eq: ["$opposite_number", "6015444"] }, then: "Info Services - 15444" },
+            { case: { $eq: ["$opposite_number", "6015777"] }, then: "Info Services - 15777" },
+            { case: { $eq: ["$opposite_number", "6015555"] }, then: "Info Services - 15555" },
+            { case: { $eq: ["$opposite_number", "6015999"] }, then: "Info Services - 15999" },
+            { case: { $eq: ["$opposite_number", "6013504"] }, then: "Info Services - 13504" },
+            { case: { $eq: ["$opposite_number", "6015511"] }, then: "Info Services - 15511" },
+            { case: { $eq: ["$opposite_number", "6015800"] }, then: "Info Services - 15800" },
+            { case: { $eq: ["$opposite_number", "6015995"] }, then: "Info Services - 15995" }
+          ],
+          default: null
+        }
+      }
+    }
+  },
+  {
+    $match: {
+      call_type: { $ne: null }
+    }
+  },
+  {
+    $group: {
+      _id: "$call_type",
+      no_of_calls: { $sum: 1 },
+      mou: {
+        $sum: {
+          $divide: [
+            { $toDouble: { $ifNull: ["$act_usage_unit", 0] } },
+            60
+          ]
+        }
+      }
+    }
+  },
+  {
+    $project: {
+      _id: 0,
+      service_type: { $literal: "Voice" },
+      charge_type: { $literal: "Premium and Special Numbers" },
+      call_type: "$_id",
+      no_of_calls: 1,
+      mou: 1,
+      sort_order: {
+        $switch: {
+          branches: [
+            { case: { $eq: ["$_id", "1 MOCC - 03-8000 8000"] }, then: 1 },
+            { case: { $eq: ["$_id", "1300 Numbers"] }, then: 2 },
+            { case: { $eq: ["$_id", "1700 Numbers"] }, then: 3 },
+            { case: { $eq: ["$_id", "1800 Numbers"] }, then: 4 },
+            { case: { $eq: ["$_id", "Directory Assistance -Services 103"] }, then: 5 },
+            { case: { $eq: ["$_id", "Info Services - 100"] }, then: 7 },
+            { case: { $eq: ["$_id", "Info Services - 15454"] }, then: 8 },
+            { case: { $eq: ["$_id", "Info Services - 15300"] }, then: 9 },
+            { case: { $eq: ["$_id", "Info Services - 15353"] }, then: 10 },
+            { case: { $eq: ["$_id", "Info Services - 15404"] }, then: 11 },
+            { case: { $eq: ["$_id", "Info Services - 15444"] }, then: 12 },
+            { case: { $eq: ["$_id", "Info Services - 15777"] }, then: 13 },
+            { case: { $eq: ["$_id", "Info Services - 15555"] }, then: 14 },
+            { case: { $eq: ["$_id", "Info Services - 15999"] }, then: 15 },
+            { case: { $eq: ["$_id", "Info Services - 13504"] }, then: 16 },
+            { case: { $eq: ["$_id", "Info Services - 15511"] }, then: 17 },
+            { case: { $eq: ["$_id", "Info Services - 15800"] }, then: 18 },
+            { case: { $eq: ["$_id", "Info Services - 15995"] }, then: 19 }
+          ],
+          default: 999
+        }
+      }
+    }
+  },
+  {
+    $addFields: {
+      mou: { $round: ["$mou", 2] }
+    }
+  },
+  {
+    $project: {
+      _id: 0,
+      service_type: 1,
+      charge_type: 1,
+      call_type: 1,
+      no_of_calls: 1,
+      mou: 1,
+      sort_order: 1
+    }
+  },
+  {
+    $sort: {
+      sort_order: 1
+    }
+  },
+  {
+    $project: {
+      sort_order: 0
+    }
+  }
+]);
+</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/eastel-report-scripts/reports-pipelines/report-generation-mongo/2-Invoice-Recon/2-Invoice-Recon-actual-queries-used-output-file.xlsx
+++ b/eastel-report-scripts/reports-pipelines/report-generation-mongo/2-Invoice-Recon/2-Invoice-Recon-actual-queries-used-output-file.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,15 +436,850 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Q014</t>
+          <t>intl.-sms</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>D:\DB_repos\eastel-reports\eastel-report-scripts\reports-pipelines\report-generation-mongo\2-Invoice-Recon\queries\14.js</t>
+          <t>D:\DB_repos\eastel-reports\eastel-report-scripts\reports-pipelines\report-generation-mongo\2-Invoice-Recon\queries\intl.-sms.js</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/*
+Query 11: International SMS by destination country.
+Equivalent PostgreSQL query:
+SELECT
+    'SMS' AS service_type,
+    'SMS MO' AS charge_type,
+    COALESCE(cc.country, 'UNMAPPED') AS country,
+    COUNT(*) AS sms_count
+FROM iot_portal_tb_usage_log t
+LEFT JOIN LATERAL (
+    SELECT c.country
+    FROM country_code c
+    WHERE TRIM(t.opposite_number::text) LIKE c.country_code || '%'
+    ORDER BY LENGTH(c.country_code) DESC
+    LIMIT 1
+) cc ON TRUE
+WHERE t.usage_start_time &gt;= '2026-04-01T00:00:00Z'
+  AND t.usage_start_time &lt; '2026-04-02T00:00:00Z'
+  AND t.rat_type = 'SM'
+  AND t.roaming_destination_id = 87
+  AND COALESCE(t.act_usage_unit, 0) &gt; 0
+  AND t.opposite_number IS NOT NULL
+  AND BTRIM(t.opposite_number::text) NOT IN ('', 'None', 'none')
+  AND BTRIM(t.opposite_number::text) NOT LIKE '60%'
+GROUP BY COALESCE(cc.country, 'UNMAPPED')
+ORDER BY country;
+Output columns:
+- service_type
+- charge_type
+- country
+- sms_count
+Included records:
+- usage_logs records within the reporting window using usage_start_time
+- rat_type = 'SM'
+- roaming_destination_id = 87
+- act_usage_unit &gt; 0
+- opposite_number present and not starting with '60'
+service_type_sub_cd = 'MO' is not required as 'MO' and 'MT' are only applicable for rat_type = 'VO' as of now, but if in future there are 'MO' and 'MT' for 'SM', we can easily add that filter back without affecting existing data since we are only looking at 'SM' records here.
+Fixed/hardcoded Output values:
+- service_type = 'SMS'
+- charge_type = 'SMS MO'
+Country is derived from the country_code collection using longest-prefix
+matching on opposite_number.
+*/
+db.usage_logs.aggregate([
+  {
+    $match: {
+      usage_start_time: {
+        $gte: ISODate("2026-04-01T00:00:00Z"),
+        $lt: ISODate("2026-04-02T00:00:00Z")
+      },
+      rat_type: "SM",
+      roaming_destination_id: 87,
+      act_usage_unit: { $gt: 0 },
+      opposite_number: { $exists: true, $ne: null }
+    }
+  },
+  {
+    $addFields: {
+      opposite_number_digits: {
+        $trim: {
+          input: { $toString: "$opposite_number" }
+        }
+      }
+    }
+  },
+  {
+    $match: {
+      opposite_number_digits: {
+        $nin: ["", "None", "none"]
+      }
+    }
+  },
+  {
+    $match: {
+      opposite_number_digits: { $not: { $regex: "^60" } }
+    }
+  },
+  {
+    $lookup: {
+      from: "country_code",
+      let: {
+        destination_number: "$opposite_number_digits"
+      },
+      pipeline: [
+        {
+          $project: {
+            _id: 0,
+            country: 1,
+            country_code_str: { $toString: "$country_code" },
+            code_length: { $strLenCP: { $toString: "$country_code" } }
+          }
+        },
+        {
+          $match: {
+            $expr: {
+              $regexMatch: {
+                input: "$$destination_number",
+                regex: { $concat: ["^", "$country_code_str"] }
+              }
+            }
+          }
+        },
+        {
+          $sort: {
+            code_length: -1
+          }
+        },
+        {
+          $limit: 1
+        }
+      ],
+      as: "country_match"
+    }
+  },
+  {
+    $addFields: {
+      country: { $ifNull: [{ $arrayElemAt: ["$country_match.country", 0] }, "UNMAPPED"] }
+    }
+  },
+  {
+    $group: {
+      _id: "$country",
+      sms_count: { $sum: 1 }
+    }
+  },
+  {
+    $project: {
+      _id: 0,
+      service_type: { $literal: "SMS" },
+      charge_type: { $literal: "SMS MO" },
+      country: "$_id",
+      sms_count: 1
+    }
+  },
+  {
+    $sort: {
+      country: 1
+    }
+  }
+]);
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>intl.-voice</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>D:\DB_repos\eastel-reports\eastel-report-scripts\reports-pipelines\report-generation-mongo\2-Invoice-Recon\queries\intl.-voice.js</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/*
+Query 12: International voice calls by destination country.
+Equivalent PostgreSQL query:
+SELECT
+    'Voice' AS service_type,
+    'Voice MO' AS charge_type,
+    COALESCE(cc.country, 'UNMAPPED') AS country,
+    COUNT(*) AS call_count,
+    ROUND(SUM(COALESCE(t.act_usage_unit, 0)) / 60.0, 2) AS mou_mins
+FROM iot_portal_tb_usage_log t
+LEFT JOIN LATERAL (
+    SELECT c.country
+    FROM country_code c
+    WHERE TRIM(t.opposite_number::text) LIKE c.country_code || '%'
+    ORDER BY LENGTH(c.country_code) DESC
+    LIMIT 1
+) cc ON TRUE
+WHERE t.usage_start_time &gt;= '2026-04-01T00:00:00Z'
+  AND t.usage_start_time &lt; '2026-04-02T00:00:00Z'
+  AND t.rat_type = 'VO'
+  AND t.service_type_sub_cd = 'MO'
+  AND t.roaming_destination_id = 87
+  AND COALESCE(t.act_usage_unit, 0) &gt; 0
+  AND t.opposite_number IS NOT NULL
+  AND BTRIM(t.opposite_number::text) NOT IN ('', 'None', 'none')
+  AND BTRIM(t.opposite_number::text) NOT LIKE '60%'
+GROUP BY COALESCE(cc.country, 'UNMAPPED')
+ORDER BY country;
+Output columns:
+- service_type
+- charge_type
+- country
+- call_count
+- mou_mins
+Included records:
+- usage_logs records within the reporting window using usage_start_time
+- rat_type = 'VO'
+- service_type_sub_cd = 'MO'
+- roaming_destination_id = 87
+- act_usage_unit &gt; 0
+- opposite_number present and not starting with '60'
+Output values:
+- service_type = 'Voice'
+- charge_type = 'Voice MO'
+Country is derived from the country_code collection using longest-prefix
+matching on opposite_number.
+*/
+db.usage_logs.aggregate([
+  {
+    $match: {
+      usage_start_time: {
+        $gte: ISODate("2026-04-01T00:00:00Z"),
+        $lt: ISODate("2026-04-02T00:00:00Z")
+      },
+      rat_type: "VO",
+      service_type_sub_cd: "MO",
+      roaming_destination_id: 87,
+      act_usage_unit: { $gt: 0 },
+      opposite_number: { $exists: true, $ne: null }
+    }
+  },
+  {
+    $addFields: {
+      opposite_number_digits: {
+        $trim: {
+          input: { $toString: "$opposite_number" }
+        }
+      }
+    }
+  },
+  {
+    $match: {
+      opposite_number_digits: {
+        $nin: ["", "None", "none"]
+      }
+    }
+  },
+  {
+    $match: {
+      opposite_number_digits: { $not: { $regex: "^60" } }
+    }
+  },
+  {
+    $lookup: {
+      from: "country_code",
+      let: {
+        destination_number: "$opposite_number_digits"
+      },
+      pipeline: [
+        {
+          $project: {
+            _id: 0,
+            country: 1,
+            country_code_str: { $toString: "$country_code" },
+            code_length: { $strLenCP: { $toString: "$country_code" } }
+          }
+        },
+        {
+          $match: {
+            $expr: {
+              $regexMatch: {
+                input: "$$destination_number",
+                regex: { $concat: ["^", "$country_code_str"] }
+              }
+            }
+          }
+        },
+        {
+          $sort: {
+            code_length: -1
+          }
+        },
+        {
+          $limit: 1
+        }
+      ],
+      as: "country_match"
+    }
+  },
+  {
+    $addFields: {
+      country: { $ifNull: [{ $arrayElemAt: ["$country_match.country", 0] }, "UNMAPPED"] }
+    }
+  },
+  {
+    $group: {
+      _id: "$country",
+      call_count: { $sum: 1 },
+      mou_mins: {
+        $sum: {
+          $divide: [
+            { $toDouble: { $ifNull: ["$act_usage_unit", 0] } },
+            60
+          ]
+        }
+      }
+    }
+  },
+  {
+    $project: {
+      _id: 0,
+      service_type: { $literal: "Voice" },
+      charge_type: { $literal: "Voice MO" },
+      country: "$_id",
+      call_count: 1,
+      mou_mins: { $round: ["$mou_mins", 2] }
+    }
+  },
+  {
+    $sort: {
+      country: 1
+    }
+  }
+]);
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>roam-data</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>D:\DB_repos\eastel-reports\eastel-report-scripts\reports-pipelines\report-generation-mongo\2-Invoice-Recon\queries\roam-data.js</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/*
+Query: Roaming data usage by country.
+Equivalent PostgreSQL query:
+SELECT
+    'Data Roaming' AS service_type,
+    'MO' AS charge_type,
+    COALESCE(
+        REPLACE(REPLACE(rd.roaming_destination_name, ': ', '-'), ':', '-'),
+        rd.country,
+        'UNMAPPED'
+    ) AS country,
+    ROUND(SUM(COALESCE(t.act_usage_unit, 0)) / 1048576.0, 2) AS usage_mbs
+FROM iot_portal_tb_usage_log t
+LEFT JOIN roaming_destination rd
+    ON rd.roaming_destination_id = t.roaming_destination_id
+WHERE t.usage_start_time &gt;= '2026-04-01T00:00:00Z'
+  AND t.usage_start_time &lt; '2026-04-02T00:00:00Z'
+  AND t.rat_type IN ('4G', '5G')
+  AND t.roaming_destination_id &lt;&gt; 87
+  AND COALESCE(t.act_usage_unit, 0) &gt; 0
+  -- rating_group 500003 is used for MCMC/MERC999 data.
+  -- Not filtering it out for now.
+GROUP BY
+    COALESCE(
+        REPLACE(REPLACE(rd.roaming_destination_name, ': ', '-'), ':', '-'),
+        rd.country,
+        'UNMAPPED'
+    )
+ORDER BY country;
+Output columns:
+- service_type
+- charge_type
+- country
+- usage_mbs
+Included records:
+- usage_logs records within the reporting window using usage_start_time
+- rat_type IN ('4G', '5G')
+- roaming_destination_id != 87
+- act_usage_unit &gt; 0
+Output values:
+- service_type = 'Data Roaming'
+- charge_type = 'MO'
+Country is derived from the roaming_destination collection.
+If roaming_destination_name exists it is normalized to Country-Network by
+replacing ':' or ': ' with '-'. If not, the country field is used.
+If neither exists, the row is labeled UNMAPPED or UNMAPPED-&lt;id&gt;.
+rating_group 500003 is used for MCMC/MERC999 data.
+It is not filtered out in this query.
+*/
+db.usage_logs.aggregate([
+  {
+    $match: {
+      usage_start_time: {
+        $gte: ISODate("2026-04-01T00:00:00Z"),
+        $lt: ISODate("2026-04-02T00:00:00Z")
+      },
+      rat_type: { $in: ["4G", "5G"] },
+      roaming_destination_id: { $ne: 87 },
+      act_usage_unit: { $gt: 0 },
+      // rating_group 500003 is used for MCMC/MERC999 data.
+      // Not filtering it out for now.
+      // rating_group: { $nin: ["500003"] }
+    }
+  },
+  {
+    $lookup: {
+      from: "roaming_destination",
+      localField: "roaming_destination_id",
+      foreignField: "roaming_destination_id",
+      as: "destination_ref"
+    }
+  },
+  {
+    $addFields: {
+      destination_ref: { $arrayElemAt: ["$destination_ref", 0] }
+    }
+  },
+  {
+    $addFields: {
+      normalized_destination_name: {
+        $replaceAll: {
+          input: {
+            $replaceAll: {
+              input: {
+                $trim: {
+                  input: { $ifNull: ["$destination_ref.roaming_destination_name", ""] }
+                }
+              },
+              find: ": ",
+              replacement: "-"
+            }
+          },
+          find: ":",
+          replacement: "-"
+        }
+      },
+      normalized_country: {
+        $trim: {
+          input: { $ifNull: ["$destination_ref.country", ""] }
+        }
+      }
+    }
+  },
+  {
+    $addFields: {
+      country: {
+        $switch: {
+          branches: [
+            {
+              case: { $ne: ["$normalized_destination_name", ""] },
+              then: "$normalized_destination_name"
+            },
+            {
+              case: { $ne: ["$normalized_country", ""] },
+              then: "$normalized_country"
+            }
+          ],
+          default: {
+            $cond: [
+              { $ne: ["$roaming_destination_id", null] },
+              { $concat: ["UNMAPPED-", { $toString: "$roaming_destination_id" }] },
+              "UNMAPPED"
+            ]
+          }
+        }
+      }
+    }
+  },
+  {
+    $group: {
+      _id: "$country",
+      usage_mbs: {
+        $sum: {
+          $divide: [
+            { $toDouble: { $ifNull: ["$act_usage_unit", 0] } },
+            1048576
+          ]
+        }
+      }
+    }
+  },
+  {
+    $project: {
+      _id: 0,
+      service_type: { $literal: "Data Roaming" },
+      charge_type: { $literal: "MO" },
+      country: "$_id",
+      usage_mbs: { $round: ["$usage_mbs", 2] }
+    }
+  },
+  {
+    $sort: {
+      country: 1
+    }
+  }
+]);
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>roam-voice</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>D:\DB_repos\eastel-reports\eastel-report-scripts\reports-pipelines\report-generation-mongo\2-Invoice-Recon\queries\roam-voice.js</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/*
+Query: Roaming voice usage by country.
+Equivalent PostgreSQL query:
+SELECT
+    'Voice Roaming' AS service_type,
+    'MO' AS charge_type,
+    COALESCE(
+        REPLACE(REPLACE(rd.roaming_destination_name, ': ', '-'), ':', '-'),
+        rd.country,
+        'UNMAPPED'
+    ) AS country,
+    COUNT(*) AS call_count,
+    ROUND(SUM(COALESCE(t.act_usage_unit, 0)) / 60.0, 2) AS mou
+FROM iot_portal_tb_usage_log t
+LEFT JOIN roaming_destination rd
+    ON rd.roaming_destination_id = t.roaming_destination_id
+WHERE t.usage_start_time &gt;= '2026-04-01T00:00:00Z'
+  AND t.usage_start_time &lt; '2026-04-02T00:00:00Z'
+  AND t.rat_type = 'VO'
+  AND t.service_type_sub_cd = 'MO'
+  AND t.roaming_destination_id &lt;&gt; 87
+  AND COALESCE(t.act_usage_unit, 0) &gt; 0
+GROUP BY
+    COALESCE(
+        REPLACE(REPLACE(rd.roaming_destination_name, ': ', '-'), ':', '-'),
+        rd.country,
+        'UNMAPPED'
+    )
+ORDER BY country;
+Output columns:
+- service_type
+- charge_type
+- country
+- call_count
+- mou
+Included records:
+- usage_logs records within the reporting window using usage_start_time
+- rat_type = 'VO'
+- service_type_sub_cd = 'MO'
+- roaming_destination_id != 87
+- act_usage_unit &gt; 0
+Output values:
+- service_type = 'Voice Roaming'
+- charge_type = 'MO'
+Country is derived from the roaming_destination collection.
+If roaming_destination_name exists it is normalized to Country-Network by
+replacing ':' or ': ' with '-'. If not, the country field is used.
+If neither exists, the row is labeled UNMAPPED or UNMAPPED-&lt;id&gt;.
+*/
+db.usage_logs.aggregate([
+  {
+    $match: {
+      usage_start_time: {
+        $gte: ISODate("2026-04-01T00:00:00Z"),
+        $lt: ISODate("2026-04-02T00:00:00Z")
+      },
+      rat_type: "VO",
+      service_type_sub_cd: "MO",
+      roaming_destination_id: { $ne: 87 },
+      act_usage_unit: { $gt: 0 }
+    }
+  },
+  {
+    $lookup: {
+      from: "roaming_destination",
+      localField: "roaming_destination_id",
+      foreignField: "roaming_destination_id",
+      as: "destination_ref"
+    }
+  },
+  {
+    $addFields: {
+      destination_ref: { $arrayElemAt: ["$destination_ref", 0] }
+    }
+  },
+  {
+    $addFields: {
+      normalized_destination_name: {
+        $replaceAll: {
+          input: {
+            $replaceAll: {
+              input: {
+                $trim: {
+                  input: { $ifNull: ["$destination_ref.roaming_destination_name", ""] }
+                }
+              },
+              find: ": ",
+              replacement: "-"
+            }
+          },
+          find: ":",
+          replacement: "-"
+        }
+      },
+      normalized_country: {
+        $trim: {
+          input: { $ifNull: ["$destination_ref.country", ""] }
+        }
+      }
+    }
+  },
+  {
+    $addFields: {
+      country: {
+        $switch: {
+          branches: [
+            {
+              case: { $ne: ["$normalized_destination_name", ""] },
+              then: "$normalized_destination_name"
+            },
+            {
+              case: { $ne: ["$normalized_country", ""] },
+              then: "$normalized_country"
+            }
+          ],
+          default: {
+            $cond: [
+              { $ne: ["$roaming_destination_id", null] },
+              { $concat: ["UNMAPPED-", { $toString: "$roaming_destination_id" }] },
+              "UNMAPPED"
+            ]
+          }
+        }
+      }
+    }
+  },
+  {
+    $group: {
+      _id: "$country",
+      call_count: { $sum: 1 },
+      mou: {
+        $sum: {
+          $divide: [
+            { $toDouble: { $ifNull: ["$act_usage_unit", 0] } },
+            60
+          ]
+        }
+      }
+    }
+  },
+  {
+    $project: {
+      _id: 0,
+      service_type: { $literal: "Voice Roaming" },
+      charge_type: { $literal: "MO" },
+      country: "$_id",
+      call_count: 1,
+      mou: { $round: ["$mou", 2] }
+    }
+  },
+  {
+    $sort: {
+      country: 1
+    }
+  }
+]);
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>roam-sms</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>D:\DB_repos\eastel-reports\eastel-report-scripts\reports-pipelines\report-generation-mongo\2-Invoice-Recon\queries\roam-sms.js</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/*
+Query: Roaming SMS usage by country.
+Equivalent PostgreSQL query:
+SELECT
+    'SMS Roaming' AS service_type,
+    'MO' AS charge_type,
+    COALESCE(
+        REPLACE(REPLACE(rd.roaming_destination_name, ': ', '-'), ':', '-'),
+        rd.country,
+        'UNMAPPED'
+    ) AS country,
+    COUNT(*) AS sms_count
+FROM iot_portal_tb_usage_log t
+LEFT JOIN roaming_destination rd
+    ON rd.roaming_destination_id = t.roaming_destination_id
+WHERE t.usage_start_time &gt;= '2026-04-01T00:00:00Z'
+  AND t.usage_start_time &lt; '2026-04-02T00:00:00Z'
+  AND t.rat_type = 'SM'
+  AND t.roaming_destination_id &lt;&gt; 87
+  AND COALESCE(t.act_usage_unit, 0) &gt; 0
+GROUP BY
+    COALESCE(
+        REPLACE(REPLACE(rd.roaming_destination_name, ': ', '-'), ':', '-'),
+        rd.country,
+        'UNMAPPED'
+    )
+ORDER BY country;
+Output columns:
+- service_type
+- charge_type
+- country
+- sms_count
+Included records:
+- usage_logs records within the reporting window using usage_start_time
+- rat_type = 'SM'
+- roaming_destination_id != 87
+- act_usage_unit &gt; 0
+Output values:
+- service_type = 'SMS Roaming'
+- charge_type = 'MO'
+Country is derived from the roaming_destination collection.
+If roaming_destination_name exists it is normalized to Country-Network by
+replacing ':' or ': ' with '-'. If not, the country field is used.
+If neither exists, the row is labeled UNMAPPED or UNMAPPED-&lt;id&gt;.
+service_type_sub_cd is not used for SMS in this dataset.
+*/
+db.usage_logs.aggregate([
+  {
+    $match: {
+      usage_start_time: {
+        $gte: ISODate("2026-04-01T00:00:00Z"),
+        $lt: ISODate("2026-04-02T00:00:00Z")
+      },
+      rat_type: "SM",
+      roaming_destination_id: { $ne: 87 },
+      act_usage_unit: { $gt: 0 }
+    }
+  },
+  {
+    $lookup: {
+      from: "roaming_destination",
+      localField: "roaming_destination_id",
+      foreignField: "roaming_destination_id",
+      as: "destination_ref"
+    }
+  },
+  {
+    $addFields: {
+      destination_ref: { $arrayElemAt: ["$destination_ref", 0] }
+    }
+  },
+  {
+    $addFields: {
+      normalized_destination_name: {
+        $replaceAll: {
+          input: {
+            $replaceAll: {
+              input: {
+                $trim: {
+                  input: { $ifNull: ["$destination_ref.roaming_destination_name", ""] }
+                }
+              },
+              find: ": ",
+              replacement: "-"
+            }
+          },
+          find: ":",
+          replacement: "-"
+        }
+      },
+      normalized_country: {
+        $trim: {
+          input: { $ifNull: ["$destination_ref.country", ""] }
+        }
+      }
+    }
+  },
+  {
+    $addFields: {
+      country: {
+        $switch: {
+          branches: [
+            {
+              case: { $ne: ["$normalized_destination_name", ""] },
+              then: "$normalized_destination_name"
+            },
+            {
+              case: { $ne: ["$normalized_country", ""] },
+              then: "$normalized_country"
+            }
+          ],
+          default: {
+            $cond: [
+              { $ne: ["$roaming_destination_id", null] },
+              { $concat: ["UNMAPPED-", { $toString: "$roaming_destination_id" }] },
+              "UNMAPPED"
+            ]
+          }
+        }
+      }
+    }
+  },
+  {
+    $group: {
+      _id: "$country",
+      sms_count: { $sum: 1 }
+    }
+  },
+  {
+    $project: {
+      _id: 0,
+      service_type: { $literal: "SMS Roaming" },
+      charge_type: { $literal: "MO" },
+      country: "$_id",
+      sms_count: 1
+    }
+  },
+  {
+    $sort: {
+      country: 1
+    }
+  }
+]);
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>premium-and-special-numbers</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>D:\DB_repos\eastel-reports\eastel-report-scripts\reports-pipelines\report-generation-mongo\2-Invoice-Recon\queries\premium-and-special-numbers.js</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t xml:space="preserve">/*
 Query 14: Premium and special numbers.
@@ -460,7 +1295,7 @@
     $match: {
       usage_start_time: {
         $gte: ISODate("2026-04-01T00:00:00Z"),
-        $lt: ISODate("2026-05-01T00:00:00Z")
+        $lt: ISODate("2026-04-02T00:00:00Z")
       },
       rat_type: "VO",
       service_type_sub_cd: "MO",
